--- a/resampling/input/accessibility_reports_generated/INTERSOS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/INTERSOS_accessibility_report.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -87,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +106,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -181,9 +184,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:O52" headerRowCount="1">
-  <autoFilter ref="A1:O52"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q52" headerRowCount="1">
+  <autoFilter ref="A1:Q52"/>
+  <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
@@ -199,15 +202,17 @@
     <tableColumn id="13" name="Reason notes"/>
     <tableColumn id="14" name="% of target achieved so far"/>
     <tableColumn id="15" name="Date reported"/>
+    <tableColumn id="16" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="17" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M84" headerRowCount="1">
-  <autoFilter ref="A1:M84"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O84" headerRowCount="1">
+  <autoFilter ref="A1:O84"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
@@ -221,6 +226,8 @@
     <tableColumn id="11" name="Reason notes"/>
     <tableColumn id="12" name="% of target achieved so far"/>
     <tableColumn id="13" name="Date reported"/>
+    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="15" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -515,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -613,58 +620,78 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Ward Accessibility</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -684,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -702,6 +729,8 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -780,6 +809,16 @@
           <t>Date reported</t>
         </is>
       </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Reported by (Partner / IMPACT-default)</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Source channel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -822,7 +861,9 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -873,7 +914,9 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -916,7 +959,9 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -959,7 +1004,9 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1002,7 +1049,9 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1045,7 +1094,9 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1088,7 +1139,9 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1131,7 +1184,9 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1174,7 +1229,9 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1217,7 +1274,9 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1268,7 +1327,9 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1311,7 +1372,9 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1354,7 +1417,9 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1397,7 +1462,9 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1440,7 +1507,9 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1483,7 +1552,9 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1526,7 +1597,9 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1577,7 +1650,9 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1628,7 +1703,9 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1679,7 +1756,9 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1722,7 +1801,9 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" s="10" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1765,7 +1846,9 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" s="10" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1816,7 +1899,9 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" s="10" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1859,7 +1944,9 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" s="10" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1902,7 +1989,9 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" s="10" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1953,7 +2042,9 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1996,7 +2087,9 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2039,7 +2132,9 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2086,7 +2181,9 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2133,7 +2230,9 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2172,7 +2271,9 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2211,7 +2312,9 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2250,7 +2353,9 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2289,7 +2394,9 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2336,7 +2443,9 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2375,7 +2484,9 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2414,7 +2525,9 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2453,7 +2566,9 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2500,7 +2615,9 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2539,7 +2656,9 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2586,7 +2705,9 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2625,7 +2746,9 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2664,7 +2787,9 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2703,7 +2828,9 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2750,7 +2877,9 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" s="10" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2789,7 +2918,9 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" s="10" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2828,7 +2959,9 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" s="10" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2875,7 +3008,9 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" s="10" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2914,7 +3049,9 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" s="10" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2953,7 +3090,9 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" s="10" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2992,15 +3131,27 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" s="10" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="K2:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-08-28</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3016,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3032,6 +3183,8 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3100,6 +3253,16 @@
           <t>Date reported</t>
         </is>
       </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Reported by (Partner / IMPACT-default)</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Source channel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3146,7 +3309,9 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3193,7 +3358,9 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3240,7 +3407,9 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3283,7 +3452,9 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3326,7 +3497,9 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3369,7 +3542,9 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3412,7 +3587,9 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3455,7 +3632,9 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3498,7 +3677,9 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3541,7 +3722,9 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3584,7 +3767,9 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3627,7 +3812,9 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3670,7 +3857,9 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3713,7 +3902,9 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3756,7 +3947,9 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3799,7 +3992,9 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3842,7 +4037,9 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3885,7 +4082,9 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3928,7 +4127,9 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3971,7 +4172,9 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4018,7 +4221,9 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4065,7 +4270,9 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4112,7 +4319,9 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4159,7 +4368,9 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4206,7 +4417,9 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4253,7 +4466,9 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4300,7 +4515,9 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4343,7 +4560,9 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4386,7 +4605,9 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4429,7 +4650,9 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4472,7 +4695,9 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4515,7 +4740,9 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4558,7 +4785,9 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4601,7 +4830,9 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4644,7 +4875,9 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4687,7 +4920,9 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4734,7 +4969,9 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4781,7 +5018,9 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4828,7 +5067,9 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4875,7 +5116,9 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4922,7 +5165,9 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4969,7 +5214,9 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5016,7 +5263,9 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5063,7 +5312,9 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5110,7 +5361,9 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" s="10" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5157,7 +5410,9 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" s="10" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5204,7 +5459,9 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5247,7 +5504,9 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5290,7 +5549,9 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" s="10" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5333,7 +5594,9 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5376,7 +5639,9 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" s="10" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5419,7 +5684,9 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" s="10" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5462,7 +5729,9 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" s="10" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5505,7 +5774,9 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5548,7 +5819,9 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5591,7 +5864,9 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5634,7 +5909,9 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" s="10" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5677,7 +5954,9 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5724,7 +6003,9 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" s="10" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5771,7 +6052,9 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" s="10" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5818,7 +6101,9 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" s="10" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5865,7 +6150,9 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" s="10" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5912,7 +6199,9 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" s="10" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5959,7 +6248,9 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" s="10" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6006,7 +6297,9 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" s="10" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6049,7 +6342,9 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6092,7 +6387,9 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" s="10" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6135,7 +6432,9 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" s="10" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6178,7 +6477,9 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" s="10" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6221,7 +6522,9 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" s="10" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6264,7 +6567,9 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" s="10" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6307,7 +6612,9 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" s="10" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6350,7 +6657,9 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" s="10" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6393,7 +6702,9 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" s="10" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6436,7 +6747,9 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" s="10" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6479,7 +6792,9 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6522,7 +6837,9 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" s="10" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6565,7 +6882,9 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="M79" s="10" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6608,7 +6927,9 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="M80" s="10" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6651,7 +6972,9 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6694,7 +7017,9 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="M82" s="10" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6737,7 +7062,9 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
+      <c r="M83" s="10" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6780,15 +7107,27 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="M84" s="10" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="I2:I84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-08-28</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6796,4 +7135,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B18C7B20-9B79-4A90-868A-9FCD8BB42671}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1A3E94-F29E-4061-B496-3018FEE232FC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4CDFF4A-DD79-42D8-B113-E2814AC43109}"/>
 </file>